--- a/甘特项目规划器.xlsx
+++ b/甘特项目规划器.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73A9A87E-A66A-4219-9212-29142487018F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1591BC-1BE3-4BAB-82E8-32FD1E4E5379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="项目规划表" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>项目规划器</t>
   </si>
@@ -53,48 +53,6 @@
   </si>
   <si>
     <t>活动</t>
-  </si>
-  <si>
-    <t>活动 05</t>
-  </si>
-  <si>
-    <t>活动 06</t>
-  </si>
-  <si>
-    <t>活动 07</t>
-  </si>
-  <si>
-    <t>活动 08</t>
-  </si>
-  <si>
-    <t>活动 09</t>
-  </si>
-  <si>
-    <t>活动 10</t>
-  </si>
-  <si>
-    <t>活动 11</t>
-  </si>
-  <si>
-    <t>活动 12</t>
-  </si>
-  <si>
-    <t>活动 13</t>
-  </si>
-  <si>
-    <t>活动 14</t>
-  </si>
-  <si>
-    <t>活动 15</t>
-  </si>
-  <si>
-    <t>活动 16</t>
-  </si>
-  <si>
-    <t>活动 17</t>
-  </si>
-  <si>
-    <t>活动 18</t>
   </si>
   <si>
     <t>计划开始时间</t>
@@ -192,11 +150,66 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>活动03</t>
+    <t>思维导图</t>
+  </si>
+  <si>
+    <t>NABCD分析</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>活动04</t>
+    <t>PC端网页原型</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动端网页原型</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>搭建开发环境</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发用户注册与登录模块</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发出题逻辑模块</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发自动批改与计时功能模块</t>
+  </si>
+  <si>
+    <t>开发题目与答案下载功能模块</t>
+  </si>
+  <si>
+    <t>开发AI出题</t>
+  </si>
+  <si>
+    <t>开发在线PK功能</t>
+  </si>
+  <si>
+    <t>前后端集成联调</t>
+  </si>
+  <si>
+    <t>功能测试</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG修复</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目官网开发</t>
+  </si>
+  <si>
+    <t>部署与发布</t>
+  </si>
+  <si>
+    <t>收集用户反馈</t>
+  </si>
+  <si>
+    <t>基于反馈修改功能</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -211,7 +224,7 @@
     <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1" tint="0.24994659260841701"/>
@@ -420,6 +433,21 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -899,7 +927,7 @@
     <xf numFmtId="0" fontId="1" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1016,6 +1044,15 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -1078,7 +1115,233 @@
     <cellStyle name="周期值" xfId="13" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="注释" xfId="32" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="26">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+        <bottom style="thin">
+          <color theme="9" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+        <bottom style="thin">
+          <color theme="9" tint="0.59996337778862885"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1465,19 +1728,19 @@
     <tabColor theme="7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:BO22"/>
-  <sheetFormatPr defaultColWidth="3.1796875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:BO24"/>
+  <sheetFormatPr defaultColWidth="3.15234375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.1796875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" style="17" customWidth="1"/>
-    <col min="3" max="6" width="11.54296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" style="19" customWidth="1"/>
-    <col min="8" max="8" width="4.08984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="27" width="3.1796875" style="3"/>
-    <col min="28" max="16384" width="3.1796875" style="4"/>
+    <col min="1" max="1" width="2.15234375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.53515625" style="17" customWidth="1"/>
+    <col min="3" max="6" width="11.53515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.53515625" style="19" customWidth="1"/>
+    <col min="8" max="8" width="4.07421875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="27" width="3.15234375" style="3"/>
+    <col min="28" max="16384" width="3.15234375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="1.25">
+    <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="1.5">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1487,7 +1750,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="2:67" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:67" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1496,34 +1759,34 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H2" s="7">
         <v>1</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="36" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L2" s="37"/>
       <c r="M2" s="38"/>
       <c r="N2" s="9"/>
       <c r="O2" s="29" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="P2" s="30"/>
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
       <c r="S2" s="10"/>
       <c r="T2" s="22" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="U2" s="23"/>
       <c r="V2" s="23"/>
       <c r="W2" s="32"/>
       <c r="X2" s="11"/>
       <c r="Y2" s="33" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="Z2" s="34"/>
       <c r="AA2" s="34"/>
@@ -1531,7 +1794,7 @@
       <c r="AC2" s="35"/>
       <c r="AD2" s="12"/>
       <c r="AE2" s="22" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AF2" s="23"/>
       <c r="AG2" s="23"/>
@@ -1541,27 +1804,27 @@
       <c r="AK2" s="23"/>
       <c r="AL2" s="23"/>
     </row>
-    <row r="3" spans="2:67" s="16" customFormat="1" ht="39.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:67" s="16" customFormat="1" ht="39.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B3" s="24" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="15"/>
@@ -1583,7 +1846,7 @@
       <c r="Z3" s="15"/>
       <c r="AA3" s="15"/>
     </row>
-    <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="25"/>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
@@ -1773,7 +2036,7 @@
     </row>
     <row r="5" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="17" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C5" s="18">
         <v>1</v>
@@ -1785,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="19">
         <v>1</v>
@@ -1793,7 +2056,7 @@
     </row>
     <row r="6" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="17" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C6" s="18">
         <v>4</v>
@@ -1813,43 +2076,77 @@
     </row>
     <row r="7" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+        <v>16</v>
+      </c>
+      <c r="C7" s="18">
+        <v>4</v>
+      </c>
+      <c r="D7" s="18">
+        <v>1</v>
+      </c>
+      <c r="E7" s="18">
+        <v>4</v>
+      </c>
+      <c r="F7" s="18">
+        <v>1</v>
+      </c>
+      <c r="G7" s="19">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="B8" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="18">
+        <v>4</v>
+      </c>
+      <c r="D8" s="18">
+        <v>1</v>
+      </c>
+      <c r="E8" s="18">
+        <v>4</v>
+      </c>
+      <c r="F8" s="18">
+        <v>1</v>
+      </c>
+      <c r="G8" s="19">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="18">
+        <v>5</v>
+      </c>
+      <c r="D9" s="18">
         <v>3</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
+      <c r="E9" s="18">
+        <v>5</v>
+      </c>
       <c r="F9" s="18"/>
     </row>
     <row r="10" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
+      <c r="B10" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="18">
+        <v>5</v>
+      </c>
+      <c r="D10" s="18">
+        <v>3</v>
+      </c>
+      <c r="E10" s="18">
+        <v>5</v>
+      </c>
       <c r="F10" s="18"/>
     </row>
     <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="17" t="s">
-        <v>5</v>
+      <c r="B11" s="39" t="s">
+        <v>19</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -1860,8 +2157,8 @@
       </c>
     </row>
     <row r="12" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="17" t="s">
-        <v>6</v>
+      <c r="B12" s="40" t="s">
+        <v>20</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -1872,8 +2169,8 @@
       </c>
     </row>
     <row r="13" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="17" t="s">
-        <v>7</v>
+      <c r="B13" s="40" t="s">
+        <v>21</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -1884,8 +2181,8 @@
       </c>
     </row>
     <row r="14" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="17" t="s">
-        <v>8</v>
+      <c r="B14" s="41" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -1896,8 +2193,8 @@
       </c>
     </row>
     <row r="15" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="17" t="s">
-        <v>9</v>
+      <c r="B15" s="41" t="s">
+        <v>23</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="18"/>
@@ -1908,8 +2205,8 @@
       </c>
     </row>
     <row r="16" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="17" t="s">
-        <v>10</v>
+      <c r="B16" s="39" t="s">
+        <v>24</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -1920,8 +2217,8 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="17" t="s">
-        <v>11</v>
+      <c r="B17" s="39" t="s">
+        <v>25</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -1932,8 +2229,8 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="17" t="s">
-        <v>12</v>
+      <c r="B18" s="39" t="s">
+        <v>26</v>
       </c>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -1944,8 +2241,8 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="17" t="s">
-        <v>13</v>
+      <c r="B19" s="39" t="s">
+        <v>27</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -1957,7 +2254,7 @@
     </row>
     <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="17" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -1968,8 +2265,8 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="17" t="s">
-        <v>15</v>
+      <c r="B21" s="39" t="s">
+        <v>29</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -1980,14 +2277,38 @@
       </c>
     </row>
     <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="17" t="s">
-        <v>16</v>
+      <c r="B22" s="39" t="s">
+        <v>30</v>
       </c>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
       <c r="G22" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19">
         <v>0</v>
       </c>
     </row>
@@ -2007,39 +2328,86 @@
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <conditionalFormatting sqref="H5:BO22">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="25" priority="17">
       <formula>完成百分比</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="24" priority="19">
       <formula>PercentCompleteBeyond</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="23" priority="20">
       <formula>实际值</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="22" priority="21">
       <formula>ActualBeyond</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="21" priority="22">
       <formula>计划</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="20" priority="23">
       <formula>H$4=period_selected</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="11">
+    <cfRule type="expression" dxfId="19" priority="27">
       <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="12">
+    <cfRule type="expression" dxfId="18" priority="28">
       <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:BO23">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>TRUE</formula>
+  <conditionalFormatting sqref="H4:BO4">
+    <cfRule type="expression" dxfId="16" priority="24">
+      <formula>H$4=period_selected</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:BO4">
+  <conditionalFormatting sqref="H23:BO23">
+    <cfRule type="expression" dxfId="15" priority="9">
+      <formula>完成百分比</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="10">
+      <formula>PercentCompleteBeyond</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>实际值</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>ActualBeyond</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="13">
+      <formula>计划</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="14">
+      <formula>H$4=period_selected</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="15">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="16">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24:BO24">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>完成百分比</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>PercentCompleteBeyond</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>实际值</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>ActualBeyond</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>计划</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>H$4=period_selected</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="0" priority="8">
-      <formula>H$4=period_selected</formula>
+      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="16">

--- a/甘特项目规划器.xlsx
+++ b/甘特项目规划器.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1591BC-1BE3-4BAB-82E8-32FD1E4E5379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E0F2AF-F0F8-42DF-9454-8CF011EF23B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="项目规划表" sheetId="1" r:id="rId1"/>
@@ -157,41 +157,14 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>PC端网页原型</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动端网页原型</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>搭建开发环境</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>开发用户注册与登录模块</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>开发出题逻辑模块</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>开发自动批改与计时功能模块</t>
-  </si>
-  <si>
-    <t>开发题目与答案下载功能模块</t>
-  </si>
-  <si>
-    <t>开发AI出题</t>
-  </si>
-  <si>
-    <t>开发在线PK功能</t>
-  </si>
-  <si>
-    <t>前后端集成联调</t>
-  </si>
-  <si>
     <t>功能测试</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
@@ -209,7 +182,39 @@
     <t>收集用户反馈</t>
   </si>
   <si>
-    <t>基于反馈修改功能</t>
+    <t>开发用户注册模块</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发用户登录模块</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发批改模块</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发导出记录模块</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发AI模块</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发在线PK模块</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>基于反馈完善</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>网页原型</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>前后端集成</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -437,18 +442,18 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1" tint="0.24994659260841701"/>
       <name val="Microsoft YaHei UI"/>
       <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1" tint="0.24994659260841701"/>
       <name val="Microsoft YaHei UI"/>
       <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="39">
@@ -994,6 +999,9 @@
     <xf numFmtId="178" fontId="27" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1045,13 +1053,10 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1115,7 +1120,7 @@
     <cellStyle name="周期值" xfId="13" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="注释" xfId="32" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill>
@@ -1358,15 +1363,6 @@
         <bottom style="thin">
           <color theme="7"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="7"/>
-        </top>
         <vertical/>
         <horizontal/>
       </border>
@@ -1729,18 +1725,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:BO24"/>
-  <sheetFormatPr defaultColWidth="3.15234375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="3.1796875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.53515625" style="17" customWidth="1"/>
-    <col min="3" max="6" width="11.53515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.53515625" style="19" customWidth="1"/>
-    <col min="8" max="8" width="4.07421875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="27" width="3.15234375" style="3"/>
-    <col min="28" max="16384" width="3.15234375" style="4"/>
+    <col min="1" max="1" width="2.1796875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" style="17" customWidth="1"/>
+    <col min="3" max="6" width="11.54296875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" style="19" customWidth="1"/>
+    <col min="8" max="8" width="4.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="27" width="3.1796875" style="3"/>
+    <col min="28" max="16384" width="3.1796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="1.5">
+    <row r="1" spans="2:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="1.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1750,7 +1746,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="2:67" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:67" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1765,62 +1761,62 @@
         <v>1</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="37"/>
-      <c r="M2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="39"/>
       <c r="N2" s="9"/>
-      <c r="O2" s="29" t="s">
+      <c r="O2" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="32"/>
       <c r="S2" s="10"/>
-      <c r="T2" s="22" t="s">
+      <c r="T2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="32"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="33"/>
       <c r="X2" s="11"/>
-      <c r="Y2" s="33" t="s">
+      <c r="Y2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="36"/>
       <c r="AD2" s="12"/>
-      <c r="AE2" s="22" t="s">
+      <c r="AE2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="AF2" s="23"/>
-      <c r="AG2" s="23"/>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="23"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
+      <c r="AH2" s="24"/>
+      <c r="AI2" s="24"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
     </row>
-    <row r="3" spans="2:67" s="16" customFormat="1" ht="39.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="24" t="s">
+    <row r="3" spans="2:67" s="16" customFormat="1" ht="39.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="29" t="s">
         <v>8</v>
       </c>
       <c r="H3" s="13" t="s">
@@ -1846,13 +1842,13 @@
       <c r="Z3" s="15"/>
       <c r="AA3" s="15"/>
     </row>
-    <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="25"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+    <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="26"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
       <c r="H4" s="21">
         <v>1</v>
       </c>
@@ -2095,7 +2091,7 @@
       </c>
     </row>
     <row r="8" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="18">
@@ -2115,161 +2111,253 @@
       </c>
     </row>
     <row r="9" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="39" t="s">
-        <v>17</v>
+      <c r="B9" s="22" t="s">
+        <v>31</v>
       </c>
       <c r="C9" s="18">
         <v>5</v>
       </c>
       <c r="D9" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="18">
         <v>5</v>
       </c>
-      <c r="F9" s="18"/>
+      <c r="F9" s="18">
+        <v>2</v>
+      </c>
+      <c r="G9" s="19">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="18">
+        <v>7</v>
+      </c>
+      <c r="D10" s="18">
+        <v>1</v>
+      </c>
+      <c r="E10" s="18">
+        <v>7</v>
+      </c>
+      <c r="F10" s="18">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="18">
+        <v>8</v>
+      </c>
+      <c r="D11" s="18">
+        <v>1</v>
+      </c>
+      <c r="E11" s="18">
+        <v>8</v>
+      </c>
+      <c r="F11" s="18">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="18">
+        <v>9</v>
+      </c>
+      <c r="D12" s="18">
+        <v>1</v>
+      </c>
+      <c r="E12" s="18">
+        <v>9</v>
+      </c>
+      <c r="F12" s="18">
+        <v>1</v>
+      </c>
+      <c r="G12" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C13" s="18">
+        <v>10</v>
+      </c>
+      <c r="D13" s="18">
+        <v>3</v>
+      </c>
+      <c r="E13" s="18">
+        <v>10</v>
+      </c>
+      <c r="F13" s="18">
         <v>5</v>
       </c>
-      <c r="D10" s="18">
-        <v>3</v>
-      </c>
-      <c r="E10" s="18">
-        <v>5</v>
-      </c>
-      <c r="F10" s="18"/>
+      <c r="G13" s="19">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="19">
-        <v>0</v>
+    <row r="14" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="18">
+        <v>13</v>
+      </c>
+      <c r="D14" s="18">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18">
+        <v>15</v>
+      </c>
+      <c r="F14" s="18">
+        <v>1</v>
+      </c>
+      <c r="G14" s="19">
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="40" t="s">
+    <row r="15" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="20">
+        <v>15</v>
+      </c>
+      <c r="D15" s="18">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18">
         <v>20</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="F15" s="18">
+        <v>1</v>
+      </c>
       <c r="G15" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="B16" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="18">
+        <v>16</v>
+      </c>
+      <c r="D16" s="18">
+        <v>2</v>
+      </c>
+      <c r="E16" s="18">
+        <v>16</v>
+      </c>
+      <c r="F16" s="18">
+        <v>2</v>
+      </c>
       <c r="G16" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
+      <c r="B17" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="18">
+        <v>17</v>
+      </c>
+      <c r="D17" s="18">
+        <v>2</v>
+      </c>
+      <c r="E17" s="18">
+        <v>17</v>
+      </c>
+      <c r="F17" s="18">
+        <v>2</v>
+      </c>
       <c r="G17" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="B18" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="18">
+        <v>19</v>
+      </c>
+      <c r="D18" s="18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="18">
+        <v>19</v>
+      </c>
+      <c r="F18" s="18">
+        <v>1</v>
+      </c>
       <c r="G18" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
+      <c r="B19" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="18">
+        <v>20</v>
+      </c>
+      <c r="D19" s="18">
+        <v>1</v>
+      </c>
+      <c r="E19" s="18">
+        <v>20</v>
+      </c>
+      <c r="F19" s="18">
+        <v>1</v>
+      </c>
       <c r="G19" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="C20" s="18">
+        <v>21</v>
+      </c>
+      <c r="D20" s="18">
+        <v>3</v>
+      </c>
+      <c r="E20" s="18">
+        <v>21</v>
+      </c>
       <c r="F20" s="18"/>
       <c r="G20" s="19">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
+      <c r="B21" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="18">
+        <v>24</v>
+      </c>
+      <c r="D21" s="18">
+        <v>1</v>
+      </c>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
       <c r="G21" s="19">
@@ -2277,11 +2365,15 @@
       </c>
     </row>
     <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
+      <c r="B22" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="18">
+        <v>24</v>
+      </c>
+      <c r="D22" s="18">
+        <v>1</v>
+      </c>
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
       <c r="G22" s="19">
@@ -2289,11 +2381,15 @@
       </c>
     </row>
     <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="B23" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="18">
+        <v>25</v>
+      </c>
+      <c r="D23" s="18">
+        <v>5</v>
+      </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
       <c r="G23" s="19">
@@ -2301,11 +2397,15 @@
       </c>
     </row>
     <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="18">
+        <v>30</v>
+      </c>
+      <c r="D24" s="18">
+        <v>3</v>
+      </c>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="19">
@@ -2328,28 +2428,28 @@
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <conditionalFormatting sqref="H5:BO22">
-    <cfRule type="expression" dxfId="25" priority="17">
+    <cfRule type="expression" dxfId="24" priority="17">
       <formula>完成百分比</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="19">
+    <cfRule type="expression" dxfId="23" priority="19">
       <formula>PercentCompleteBeyond</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="20">
+    <cfRule type="expression" dxfId="22" priority="20">
       <formula>实际值</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="21">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>ActualBeyond</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="20" priority="22">
       <formula>计划</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="23">
+    <cfRule type="expression" dxfId="19" priority="23">
       <formula>H$4=period_selected</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="27">
+    <cfRule type="expression" dxfId="18" priority="27">
       <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="28">
+    <cfRule type="expression" dxfId="17" priority="28">
       <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/甘特项目规划器.xlsx
+++ b/甘特项目规划器.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E0F2AF-F0F8-42DF-9454-8CF011EF23B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7284A80-7DE0-449A-83BD-28683C7BAF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,6 +1002,12 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1052,12 +1058,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -1761,62 +1761,62 @@
         <v>1</v>
       </c>
       <c r="J2" s="8"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="38"/>
-      <c r="M2" s="39"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="41"/>
       <c r="N2" s="9"/>
-      <c r="O2" s="30" t="s">
+      <c r="O2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="32"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="34"/>
       <c r="S2" s="10"/>
-      <c r="T2" s="23" t="s">
+      <c r="T2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="33"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="35"/>
       <c r="X2" s="11"/>
-      <c r="Y2" s="34" t="s">
+      <c r="Y2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="36"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="38"/>
       <c r="AD2" s="12"/>
-      <c r="AE2" s="23" t="s">
+      <c r="AE2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26"/>
+      <c r="AH2" s="26"/>
+      <c r="AI2" s="26"/>
+      <c r="AJ2" s="26"/>
+      <c r="AK2" s="26"/>
+      <c r="AL2" s="26"/>
     </row>
     <row r="3" spans="2:67" s="16" customFormat="1" ht="39.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="31" t="s">
         <v>8</v>
       </c>
       <c r="H3" s="13" t="s">
@@ -1843,12 +1843,12 @@
       <c r="AA3" s="15"/>
     </row>
     <row r="4" spans="2:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="26"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="21">
         <v>1</v>
       </c>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="11" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="23" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="18">
@@ -2171,7 +2171,7 @@
       </c>
     </row>
     <row r="12" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="18">
@@ -2191,7 +2191,7 @@
       </c>
     </row>
     <row r="13" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="18">
@@ -2211,7 +2211,7 @@
       </c>
     </row>
     <row r="14" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="23" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="18">
@@ -2231,7 +2231,7 @@
       </c>
     </row>
     <row r="15" spans="2:67" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="20">
@@ -2338,14 +2338,16 @@
         <v>21</v>
       </c>
       <c r="D20" s="18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="18">
         <v>21</v>
       </c>
-      <c r="F20" s="18"/>
+      <c r="F20" s="18">
+        <v>5</v>
+      </c>
       <c r="G20" s="19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -2358,10 +2360,14 @@
       <c r="D21" s="18">
         <v>1</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="E21" s="18">
+        <v>24</v>
+      </c>
+      <c r="F21" s="18">
+        <v>1</v>
+      </c>
       <c r="G21" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -2369,15 +2375,19 @@
         <v>22</v>
       </c>
       <c r="C22" s="18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" s="18">
         <v>1</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+      <c r="E22" s="18">
+        <v>25</v>
+      </c>
+      <c r="F22" s="18">
+        <v>1</v>
+      </c>
       <c r="G22" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -2385,15 +2395,19 @@
         <v>23</v>
       </c>
       <c r="C23" s="18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" s="18">
-        <v>5</v>
-      </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="E23" s="18">
+        <v>26</v>
+      </c>
+      <c r="F23" s="18">
+        <v>4</v>
+      </c>
       <c r="G23" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -2406,10 +2420,14 @@
       <c r="D24" s="18">
         <v>3</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="E24" s="18">
+        <v>30</v>
+      </c>
+      <c r="F24" s="18">
+        <v>3</v>
+      </c>
       <c r="G24" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
